--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E146B522-F4C1-4A6B-950A-33AEA84A9154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9759531AAADA9285486318E5670D88ADA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A9B8A0F-9DB3-4B8A-98E3-015B56256EB2}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 09-09-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 14-09-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -461,9 +461,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,7 +495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -527,7 +527,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -559,7 +559,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -591,7 +591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -623,7 +623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -655,7 +655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -687,7 +687,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -719,7 +719,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -751,7 +751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -783,7 +783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -815,7 +815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -847,7 +847,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -879,7 +879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9759531AAADA9285486318E5670D88ADA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A9B8A0F-9DB3-4B8A-98E3-015B56256EB2}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9759531AAADA9288E8E34B49471D88ADA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17F9E52E-FB07-4E6B-934C-C19B273999B6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9759531AAADA9288E8E34B49471D88ADA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17F9E52E-FB07-4E6B-934C-C19B273999B6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A05F0E-5A4F-4036-80B9-8ACAAE32B14F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -461,9 +461,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,7 +495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -527,7 +527,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -559,7 +559,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -591,7 +591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -623,7 +623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -655,7 +655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -687,7 +687,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -719,7 +719,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -751,7 +751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -783,7 +783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -815,7 +815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -847,7 +847,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -879,7 +879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A05F0E-5A4F-4036-80B9-8ACAAE32B14F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0CF4D3-3E30-4617-AFAF-281F64FC1DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 14-09-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 17-09-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -461,9 +461,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,7 +495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -527,7 +527,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -559,7 +559,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -591,7 +591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -623,7 +623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -655,7 +655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -687,7 +687,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -719,7 +719,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -751,7 +751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -783,7 +783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -815,7 +815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -847,7 +847,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -879,7 +879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0CF4D3-3E30-4617-AFAF-281F64FC1DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F078592F-5A11-441A-AE40-5A83B2F58F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F078592F-5A11-441A-AE40-5A83B2F58F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9759531AAADA928007E73B5CC71D88ADA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0733CB39-1165-44BE-96C7-766ECE7237FA}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 17-09-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 18-09-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -461,9 +461,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,7 +495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -527,7 +527,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -559,7 +559,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -591,7 +591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -623,7 +623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -655,7 +655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -687,7 +687,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -719,7 +719,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -751,7 +751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -783,7 +783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -815,7 +815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -847,7 +847,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -879,7 +879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9759531AAADA928007E73B5CC71D88ADA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0733CB39-1165-44BE-96C7-766ECE7237FA}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9759531AAADA9288226B1A39E71D88ADA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06611C4F-9C60-49DC-BF64-C83C0C7D025F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 18-09-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 21-09-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9759531AAADA9288226B1A39E71D88ADA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06611C4F-9C60-49DC-BF64-C83C0C7D025F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39451BBB-B17D-42D8-838E-79C9945599CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
@@ -461,9 +461,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,7 +495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -527,7 +527,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -559,7 +559,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -591,7 +591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -623,7 +623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -655,7 +655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -687,7 +687,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -719,7 +719,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -751,7 +751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -783,7 +783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -815,7 +815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -847,7 +847,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -879,7 +879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39451BBB-B17D-42D8-838E-79C9945599CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BCC3416-D9D2-4B83-A461-D9AF7C98A7CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 21-09-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 22-09-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BCC3416-D9D2-4B83-A461-D9AF7C98A7CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9510F948-0F4C-4FB2-9C43-C1DDEB7789B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9510F948-0F4C-4FB2-9C43-C1DDEB7789B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35EE1BF3-50F5-4470-989E-8E13E2C287B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 22-09-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 23-09-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35EE1BF3-50F5-4470-989E-8E13E2C287B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9759531AAADA928F9E6B5994C70D88ADA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{301E7E17-7E63-40BF-94EB-02196A8F81F2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
@@ -461,9 +461,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,7 +495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -527,7 +527,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -559,7 +559,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -591,7 +591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -623,7 +623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -655,7 +655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -687,7 +687,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -719,7 +719,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -751,7 +751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -783,7 +783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -815,7 +815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -847,7 +847,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -879,7 +879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9759531AAADA928F9E6B5994C70D88ADA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{301E7E17-7E63-40BF-94EB-02196A8F81F2}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9759531AAADA9289FBE3791C271D88ADA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0ABCA3C8-73DC-4AFB-BB5C-1836288162BA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 23-09-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 24-09-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9759531AAADA9289FBE3791C271D88ADA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0ABCA3C8-73DC-4AFB-BB5C-1836288162BA}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9759531AAADA928EB6EF6BDD470D88ADA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6A46EBD-3108-4BC9-A12B-8DC7A77150D6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9759531AAADA928EB6EF6BDD470D88ADA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6A46EBD-3108-4BC9-A12B-8DC7A77150D6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C63ADF-3044-40FD-BDF9-A56D28DF43AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 24-09-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 28-09-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -461,9 +461,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,7 +495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -527,7 +527,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -559,7 +559,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -591,7 +591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -623,7 +623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -655,7 +655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -687,7 +687,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -719,7 +719,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -751,7 +751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -783,7 +783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -815,7 +815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -847,7 +847,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -879,7 +879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C63ADF-3044-40FD-BDF9-A56D28DF43AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9759531AAADA928D87EF0AEA070D88ADA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBC0F167-77D6-4480-BCB2-19C97CF6697B}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 28-09-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 02-10-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -461,9 +461,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,7 +495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -527,7 +527,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -559,7 +559,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -591,7 +591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -623,7 +623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -655,7 +655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -687,7 +687,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -719,7 +719,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -751,7 +751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -783,7 +783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -815,7 +815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -847,7 +847,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -879,7 +879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9510F948-0F4C-4FB2-9C43-C1DDEB7789B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13ACD1D-5699-4AA6-A265-E61BA8CC33F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 22-09-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 07-10-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9759531AAADA928D87EF0AEA070D88ADA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBC0F167-77D6-4480-BCB2-19C97CF6697B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF18B3A-7770-419D-A206-24FECA97EBFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 02-10-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 07-10-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -461,9 +461,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,7 +495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -527,7 +527,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -559,7 +559,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -591,7 +591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -623,7 +623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -655,7 +655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -687,7 +687,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -719,7 +719,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -751,7 +751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -783,7 +783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -815,7 +815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -847,7 +847,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -879,7 +879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF18B3A-7770-419D-A206-24FECA97EBFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9759531AAADA92806FEB5B39471D88AA6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18054F84-9E31-4A73-A8A5-C11141F93EA2}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 07-10-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 08-10-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9759531AAADA92806FEB5B39471D88AA6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18054F84-9E31-4A73-A8A5-C11141F93EA2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2907AA9B-62B7-473E-94EB-A85E3AE5B25F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 08-10-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 09-10-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2907AA9B-62B7-473E-94EB-A85E3AE5B25F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AF2C056-96F9-46DD-A54E-E6628AA35A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sundhedscentersystemer_excel.XLSX
+++ b/html/Sundhedscentersystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AF2C056-96F9-46DD-A54E-E6628AA35A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9759531AAADA9289B7E71BCEC70D88AA6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87436B56-5A6F-42A6-B753-18A9BA2BB72B}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sundhedscentersystemer">'Opdateret d. 09-10-2026'!$A$1:$J$14</definedName>
+    <definedName name="Sundhedscentersystemer">'Opdateret d. 23-10-2026'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
